--- a/artfynd/A 22839-2025 artfynd.xlsx
+++ b/artfynd/A 22839-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136476002</v>
       </c>
       <c r="B2" t="n">
-        <v>98363</v>
+        <v>98366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136496576</v>
       </c>
       <c r="B3" t="n">
-        <v>98770</v>
+        <v>98773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136496814</v>
       </c>
       <c r="B4" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22839-2025 artfynd.xlsx
+++ b/artfynd/A 22839-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136476002</v>
       </c>
       <c r="B2" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136496576</v>
       </c>
       <c r="B3" t="n">
-        <v>98773</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136496814</v>
       </c>
       <c r="B4" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22839-2025 artfynd.xlsx
+++ b/artfynd/A 22839-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136476002</v>
       </c>
       <c r="B2" t="n">
-        <v>98367</v>
+        <v>98372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136496576</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>98779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136496814</v>
       </c>
       <c r="B4" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22839-2025 artfynd.xlsx
+++ b/artfynd/A 22839-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136476002</v>
       </c>
       <c r="B2" t="n">
-        <v>98372</v>
+        <v>98374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136496576</v>
       </c>
       <c r="B3" t="n">
-        <v>98779</v>
+        <v>98781</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136496814</v>
       </c>
       <c r="B4" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22839-2025 artfynd.xlsx
+++ b/artfynd/A 22839-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136476002</v>
       </c>
       <c r="B2" t="n">
-        <v>98374</v>
+        <v>98380</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136496576</v>
       </c>
       <c r="B3" t="n">
-        <v>98781</v>
+        <v>98787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136496814</v>
       </c>
       <c r="B4" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22839-2025 artfynd.xlsx
+++ b/artfynd/A 22839-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136476002</v>
       </c>
       <c r="B2" t="n">
-        <v>98380</v>
+        <v>98382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136496576</v>
       </c>
       <c r="B3" t="n">
-        <v>98787</v>
+        <v>98789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136496814</v>
       </c>
       <c r="B4" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22839-2025 artfynd.xlsx
+++ b/artfynd/A 22839-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136476002</v>
       </c>
       <c r="B2" t="n">
-        <v>98382</v>
+        <v>98383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136496576</v>
       </c>
       <c r="B3" t="n">
-        <v>98789</v>
+        <v>98790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136496814</v>
       </c>
       <c r="B4" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22839-2025 artfynd.xlsx
+++ b/artfynd/A 22839-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136476002</v>
       </c>
       <c r="B2" t="n">
-        <v>98383</v>
+        <v>98389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136496576</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>98796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136496814</v>
       </c>
       <c r="B4" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22839-2025 artfynd.xlsx
+++ b/artfynd/A 22839-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136496576</v>
       </c>
       <c r="B3" t="n">
-        <v>98796</v>
+        <v>98800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136496814</v>
       </c>
       <c r="B4" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
